--- a/Prevalence_of_dementia_2024_tidy.xlsx
+++ b/Prevalence_of_dementia_2024_tidy.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5052e625e7f51e50/Desktop/health-data-dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSI\OneDrive\Desktop\health-data-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95DACA35-E409-48F7-AECE-999A55B6A048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3DC71C-A242-467E-8D56-F18D7FDDD452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="2580" windowWidth="17280" windowHeight="8880" xr2:uid="{0A14B364-B9D4-44D8-BAB1-B7F6500102B6}"/>
+    <workbookView xWindow="1644" yWindow="1980" windowWidth="17280" windowHeight="8880" xr2:uid="{0A14B364-B9D4-44D8-BAB1-B7F6500102B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>30–59</t>
   </si>
@@ -67,15 +67,22 @@
   </si>
   <si>
     <t>Female</t>
+  </si>
+  <si>
+    <t>Male_rate</t>
+  </si>
+  <si>
+    <t>Female_rate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -155,7 +162,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -169,9 +176,11 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="AIHW Caption" xfId="1" xr:uid="{298087E3-0DF6-4593-9C5E-30FF3A225D5E}"/>
@@ -490,13 +499,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3313AE49-AF66-46C0-920D-D58E998B722A}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -506,93 +515,147 @@
       <c r="C1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4">
         <v>2988</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="2">
         <v>2588</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" s="6">
+        <v>0.56343466109999996</v>
+      </c>
+      <c r="E2" s="7">
+        <v>0.47719127239999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="3">
         <v>10428</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="2">
         <v>13192</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="5">
+        <v>13.9625</v>
+      </c>
+      <c r="E3" s="7">
+        <v>16.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="3">
         <v>14361</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="2">
         <v>19328</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="5">
+        <v>21.995475113099999</v>
+      </c>
+      <c r="E4" s="7">
+        <v>27.351432880800001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="3">
         <v>20051</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="2">
         <v>28032</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" s="5">
+        <v>35.800387596900002</v>
+      </c>
+      <c r="E5" s="7">
+        <v>45.653100775200002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="3">
         <v>28463</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="2">
         <v>40329</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" s="5">
+        <v>61.293559240599997</v>
+      </c>
+      <c r="E6" s="7">
+        <v>79.265681326600003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="3">
         <v>29539</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="2">
         <v>45840</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" s="5">
+        <v>104.2793670116</v>
+      </c>
+      <c r="E7" s="7">
+        <v>139.43051328870001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="3">
         <v>26862</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="2">
         <v>49171</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" s="5">
+        <v>173.0569020559</v>
+      </c>
+      <c r="E8" s="7">
+        <v>236.54395351810001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="2">
         <v>26460</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="2">
         <v>67045</v>
+      </c>
+      <c r="D9" s="5">
+        <v>337.03534499419999</v>
+      </c>
+      <c r="E9" s="7">
+        <v>479.19953735019999</v>
       </c>
     </row>
   </sheetData>
